--- a/DawesRollsViewer/Dawes Rolls One Document/Chickasaw/Chickasaw Newborn.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Chickasaw/Chickasaw Newborn.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -387,10 +390,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,6 +435,9 @@
       </c>
       <c r="N1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/DawesRollsViewer/Dawes Rolls One Document/Chickasaw/Chickasaw Newborn.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Chickasaw/Chickasaw Newborn.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O579"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -440,6 +440,3473 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" spans="1:15">
+      <c r="A2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4">
+        <f t="shared" ref="A4:A67" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <f t="shared" ref="A68:A131" si="1">A67+1</f>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <f t="shared" si="1"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <f t="shared" si="1"/>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <f t="shared" si="1"/>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <f t="shared" si="1"/>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <f t="shared" si="1"/>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <f t="shared" si="1"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <f t="shared" si="1"/>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <f t="shared" ref="A132:A195" si="2">A131+1</f>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <f t="shared" si="2"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <f t="shared" si="2"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <f t="shared" si="2"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <f t="shared" si="2"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <f t="shared" si="2"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <f t="shared" si="2"/>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <f t="shared" si="2"/>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <f t="shared" si="2"/>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <f t="shared" si="2"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <f t="shared" si="2"/>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <f t="shared" si="2"/>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <f t="shared" si="2"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <f t="shared" si="2"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <f t="shared" si="2"/>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <f t="shared" si="2"/>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <f t="shared" si="2"/>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <f t="shared" si="2"/>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <f t="shared" si="2"/>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <f t="shared" si="2"/>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <f t="shared" si="2"/>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <f t="shared" si="2"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <f t="shared" si="2"/>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <f t="shared" si="2"/>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <f t="shared" si="2"/>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <f t="shared" si="2"/>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <f t="shared" si="2"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <f t="shared" si="2"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <f t="shared" si="2"/>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <f t="shared" si="2"/>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <f t="shared" si="2"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <f t="shared" si="2"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <f t="shared" si="2"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <f t="shared" si="2"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <f t="shared" si="2"/>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <f t="shared" si="2"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <f t="shared" si="2"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <f t="shared" si="2"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <f t="shared" si="2"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <f t="shared" si="2"/>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <f t="shared" si="2"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <f t="shared" si="2"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <f t="shared" si="2"/>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <f t="shared" si="2"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <f t="shared" si="2"/>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <f t="shared" si="2"/>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <f t="shared" si="2"/>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <f t="shared" si="2"/>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <f t="shared" si="2"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <f t="shared" si="2"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <f t="shared" si="2"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <f t="shared" si="2"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <f t="shared" si="2"/>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <f t="shared" si="2"/>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191">
+        <f t="shared" si="2"/>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <f t="shared" si="2"/>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
+        <f t="shared" si="2"/>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194">
+        <f t="shared" si="2"/>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195">
+        <f t="shared" si="2"/>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196">
+        <f t="shared" ref="A196:A259" si="3">A195+1</f>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <f t="shared" si="3"/>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
+        <f t="shared" si="3"/>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199">
+        <f t="shared" si="3"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200">
+        <f t="shared" si="3"/>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202">
+        <f t="shared" si="3"/>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203">
+        <f t="shared" si="3"/>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204">
+        <f t="shared" si="3"/>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205">
+        <f t="shared" si="3"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206">
+        <f t="shared" si="3"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207">
+        <f t="shared" si="3"/>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208">
+        <f t="shared" si="3"/>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209">
+        <f t="shared" si="3"/>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210">
+        <f t="shared" si="3"/>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211">
+        <f t="shared" si="3"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212">
+        <f t="shared" si="3"/>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213">
+        <f t="shared" si="3"/>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214">
+        <f t="shared" si="3"/>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215">
+        <f t="shared" si="3"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217">
+        <f t="shared" si="3"/>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218">
+        <f t="shared" si="3"/>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219">
+        <f t="shared" si="3"/>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220">
+        <f t="shared" si="3"/>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221">
+        <f t="shared" si="3"/>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222">
+        <f t="shared" si="3"/>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223">
+        <f t="shared" si="3"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224">
+        <f t="shared" si="3"/>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <f t="shared" si="3"/>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <f t="shared" si="3"/>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <f t="shared" si="3"/>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <f t="shared" si="3"/>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <f t="shared" si="3"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <f t="shared" si="3"/>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <f t="shared" si="3"/>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <f t="shared" si="3"/>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <f t="shared" si="3"/>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <f t="shared" si="3"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <f t="shared" si="3"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <f t="shared" si="3"/>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <f t="shared" si="3"/>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <f t="shared" si="3"/>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <f t="shared" si="3"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <f t="shared" si="3"/>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <f t="shared" si="3"/>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <f t="shared" si="3"/>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <f t="shared" si="3"/>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <f t="shared" si="3"/>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <f t="shared" si="3"/>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <f t="shared" si="3"/>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <f t="shared" si="3"/>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <f t="shared" si="3"/>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <f t="shared" si="3"/>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <f t="shared" si="3"/>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <f t="shared" si="3"/>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <f t="shared" si="3"/>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <f t="shared" si="3"/>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <f t="shared" si="3"/>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <f t="shared" si="3"/>
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <f t="shared" ref="A260:A323" si="4">A259+1</f>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <f t="shared" si="4"/>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <f t="shared" si="4"/>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <f t="shared" si="4"/>
+        <v>263</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <f t="shared" si="4"/>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <f t="shared" si="4"/>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <f t="shared" si="4"/>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <f t="shared" si="4"/>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <f t="shared" si="4"/>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <f t="shared" si="4"/>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271">
+        <f t="shared" si="4"/>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272">
+        <f t="shared" si="4"/>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273">
+        <f t="shared" si="4"/>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274">
+        <f t="shared" si="4"/>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275">
+        <f t="shared" si="4"/>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276">
+        <f t="shared" si="4"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277">
+        <f t="shared" si="4"/>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278">
+        <f t="shared" si="4"/>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279">
+        <f t="shared" si="4"/>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280">
+        <f t="shared" si="4"/>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281">
+        <f t="shared" si="4"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282">
+        <f t="shared" si="4"/>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283">
+        <f t="shared" si="4"/>
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284">
+        <f t="shared" si="4"/>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285">
+        <f t="shared" si="4"/>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286">
+        <f t="shared" si="4"/>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287">
+        <f t="shared" si="4"/>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288">
+        <f t="shared" si="4"/>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290">
+        <f t="shared" si="4"/>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291">
+        <f t="shared" si="4"/>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292">
+        <f t="shared" si="4"/>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293">
+        <f t="shared" si="4"/>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294">
+        <f t="shared" si="4"/>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295">
+        <f t="shared" si="4"/>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296">
+        <f t="shared" si="4"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297">
+        <f t="shared" si="4"/>
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298">
+        <f t="shared" si="4"/>
+        <v>297</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299">
+        <f t="shared" si="4"/>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300">
+        <f t="shared" si="4"/>
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302">
+        <f t="shared" si="4"/>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303">
+        <f t="shared" si="4"/>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304">
+        <f t="shared" si="4"/>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305">
+        <f t="shared" si="4"/>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306">
+        <f t="shared" si="4"/>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307">
+        <f t="shared" si="4"/>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308">
+        <f t="shared" si="4"/>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309">
+        <f t="shared" si="4"/>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310">
+        <f t="shared" si="4"/>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311">
+        <f t="shared" si="4"/>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312">
+        <f t="shared" si="4"/>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313">
+        <f t="shared" si="4"/>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314">
+        <f t="shared" si="4"/>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315">
+        <f t="shared" si="4"/>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316">
+        <f t="shared" si="4"/>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317">
+        <f t="shared" si="4"/>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318">
+        <f t="shared" si="4"/>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319">
+        <f t="shared" si="4"/>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320">
+        <f t="shared" si="4"/>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321">
+        <f t="shared" si="4"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322">
+        <f t="shared" si="4"/>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323">
+        <f t="shared" si="4"/>
+        <v>322</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324">
+        <f t="shared" ref="A324:A387" si="5">A323+1</f>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325">
+        <f t="shared" si="5"/>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326">
+        <f t="shared" si="5"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327">
+        <f t="shared" si="5"/>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328">
+        <f t="shared" si="5"/>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329">
+        <f t="shared" si="5"/>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330">
+        <f t="shared" si="5"/>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331">
+        <f t="shared" si="5"/>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332">
+        <f t="shared" si="5"/>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333">
+        <f t="shared" si="5"/>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334">
+        <f t="shared" si="5"/>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335">
+        <f t="shared" si="5"/>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336">
+        <f t="shared" si="5"/>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337">
+        <f t="shared" si="5"/>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338">
+        <f t="shared" si="5"/>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339">
+        <f t="shared" si="5"/>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340">
+        <f t="shared" si="5"/>
+        <v>339</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341">
+        <f t="shared" si="5"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342">
+        <f t="shared" si="5"/>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343">
+        <f t="shared" si="5"/>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344">
+        <f t="shared" si="5"/>
+        <v>343</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345">
+        <f t="shared" si="5"/>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346">
+        <f t="shared" si="5"/>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347">
+        <f t="shared" si="5"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348">
+        <f t="shared" si="5"/>
+        <v>347</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349">
+        <f t="shared" si="5"/>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350">
+        <f t="shared" si="5"/>
+        <v>349</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351">
+        <f t="shared" si="5"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352">
+        <f t="shared" si="5"/>
+        <v>351</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353">
+        <f t="shared" si="5"/>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354">
+        <f t="shared" si="5"/>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355">
+        <f t="shared" si="5"/>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356">
+        <f t="shared" si="5"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357">
+        <f t="shared" si="5"/>
+        <v>356</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358">
+        <f t="shared" si="5"/>
+        <v>357</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359">
+        <f t="shared" si="5"/>
+        <v>358</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360">
+        <f t="shared" si="5"/>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361">
+        <f t="shared" si="5"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362">
+        <f t="shared" si="5"/>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363">
+        <f t="shared" si="5"/>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364">
+        <f t="shared" si="5"/>
+        <v>363</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365">
+        <f t="shared" si="5"/>
+        <v>364</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366">
+        <f t="shared" si="5"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367">
+        <f t="shared" si="5"/>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368">
+        <f t="shared" si="5"/>
+        <v>367</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369">
+        <f t="shared" si="5"/>
+        <v>368</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370">
+        <f t="shared" si="5"/>
+        <v>369</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371">
+        <f t="shared" si="5"/>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372">
+        <f t="shared" si="5"/>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373">
+        <f t="shared" si="5"/>
+        <v>372</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374">
+        <f t="shared" si="5"/>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375">
+        <f t="shared" si="5"/>
+        <v>374</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376">
+        <f t="shared" si="5"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377">
+        <f t="shared" si="5"/>
+        <v>376</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378">
+        <f t="shared" si="5"/>
+        <v>377</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379">
+        <f t="shared" si="5"/>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380">
+        <f t="shared" si="5"/>
+        <v>379</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381">
+        <f t="shared" si="5"/>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382">
+        <f t="shared" si="5"/>
+        <v>381</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383">
+        <f t="shared" si="5"/>
+        <v>382</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384">
+        <f t="shared" si="5"/>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385">
+        <f t="shared" si="5"/>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386">
+        <f t="shared" si="5"/>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387">
+        <f t="shared" si="5"/>
+        <v>386</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388">
+        <f t="shared" ref="A388:A451" si="6">A387+1</f>
+        <v>387</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389">
+        <f t="shared" si="6"/>
+        <v>388</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390">
+        <f t="shared" si="6"/>
+        <v>389</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391">
+        <f t="shared" si="6"/>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392">
+        <f t="shared" si="6"/>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393">
+        <f t="shared" si="6"/>
+        <v>392</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394">
+        <f t="shared" si="6"/>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395">
+        <f t="shared" si="6"/>
+        <v>394</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396">
+        <f t="shared" si="6"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397">
+        <f t="shared" si="6"/>
+        <v>396</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398">
+        <f t="shared" si="6"/>
+        <v>397</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399">
+        <f t="shared" si="6"/>
+        <v>398</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400">
+        <f t="shared" si="6"/>
+        <v>399</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402">
+        <f t="shared" si="6"/>
+        <v>401</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403">
+        <f t="shared" si="6"/>
+        <v>402</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404">
+        <f t="shared" si="6"/>
+        <v>403</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405">
+        <f t="shared" si="6"/>
+        <v>404</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406">
+        <f t="shared" si="6"/>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407">
+        <f t="shared" si="6"/>
+        <v>406</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408">
+        <f t="shared" si="6"/>
+        <v>407</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409">
+        <f t="shared" si="6"/>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410">
+        <f t="shared" si="6"/>
+        <v>409</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411">
+        <f t="shared" si="6"/>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412">
+        <f t="shared" si="6"/>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413">
+        <f t="shared" si="6"/>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414">
+        <f t="shared" si="6"/>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415">
+        <f t="shared" si="6"/>
+        <v>414</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416">
+        <f t="shared" si="6"/>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417">
+        <f t="shared" si="6"/>
+        <v>416</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418">
+        <f t="shared" si="6"/>
+        <v>417</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419">
+        <f t="shared" si="6"/>
+        <v>418</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420">
+        <f t="shared" si="6"/>
+        <v>419</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421">
+        <f t="shared" si="6"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422">
+        <f t="shared" si="6"/>
+        <v>421</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423">
+        <f t="shared" si="6"/>
+        <v>422</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424">
+        <f t="shared" si="6"/>
+        <v>423</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425">
+        <f t="shared" si="6"/>
+        <v>424</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426">
+        <f t="shared" si="6"/>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427">
+        <f t="shared" si="6"/>
+        <v>426</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428">
+        <f t="shared" si="6"/>
+        <v>427</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429">
+        <f t="shared" si="6"/>
+        <v>428</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430">
+        <f t="shared" si="6"/>
+        <v>429</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431">
+        <f t="shared" si="6"/>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432">
+        <f t="shared" si="6"/>
+        <v>431</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433">
+        <f t="shared" si="6"/>
+        <v>432</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434">
+        <f t="shared" si="6"/>
+        <v>433</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435">
+        <f t="shared" si="6"/>
+        <v>434</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436">
+        <f t="shared" si="6"/>
+        <v>435</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437">
+        <f t="shared" si="6"/>
+        <v>436</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438">
+        <f t="shared" si="6"/>
+        <v>437</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439">
+        <f t="shared" si="6"/>
+        <v>438</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440">
+        <f t="shared" si="6"/>
+        <v>439</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441">
+        <f t="shared" si="6"/>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442">
+        <f t="shared" si="6"/>
+        <v>441</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443">
+        <f t="shared" si="6"/>
+        <v>442</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1">
+      <c r="A444">
+        <f t="shared" si="6"/>
+        <v>443</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445">
+        <f t="shared" si="6"/>
+        <v>444</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1">
+      <c r="A446">
+        <f t="shared" si="6"/>
+        <v>445</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447">
+        <f t="shared" si="6"/>
+        <v>446</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448">
+        <f t="shared" si="6"/>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449">
+        <f t="shared" si="6"/>
+        <v>448</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450">
+        <f t="shared" si="6"/>
+        <v>449</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451">
+        <f t="shared" si="6"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452">
+        <f t="shared" ref="A452:A515" si="7">A451+1</f>
+        <v>451</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453">
+        <f t="shared" si="7"/>
+        <v>452</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454">
+        <f t="shared" si="7"/>
+        <v>453</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455">
+        <f t="shared" si="7"/>
+        <v>454</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456">
+        <f t="shared" si="7"/>
+        <v>455</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457">
+        <f t="shared" si="7"/>
+        <v>456</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458">
+        <f t="shared" si="7"/>
+        <v>457</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459">
+        <f t="shared" si="7"/>
+        <v>458</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1">
+      <c r="A460">
+        <f t="shared" si="7"/>
+        <v>459</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1">
+      <c r="A461">
+        <f t="shared" si="7"/>
+        <v>460</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1">
+      <c r="A462">
+        <f t="shared" si="7"/>
+        <v>461</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1">
+      <c r="A463">
+        <f t="shared" si="7"/>
+        <v>462</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1">
+      <c r="A464">
+        <f t="shared" si="7"/>
+        <v>463</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1">
+      <c r="A465">
+        <f t="shared" si="7"/>
+        <v>464</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1">
+      <c r="A466">
+        <f t="shared" si="7"/>
+        <v>465</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1">
+      <c r="A467">
+        <f t="shared" si="7"/>
+        <v>466</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1">
+      <c r="A468">
+        <f t="shared" si="7"/>
+        <v>467</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1">
+      <c r="A469">
+        <f t="shared" si="7"/>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1">
+      <c r="A470">
+        <f t="shared" si="7"/>
+        <v>469</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1">
+      <c r="A471">
+        <f t="shared" si="7"/>
+        <v>470</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1">
+      <c r="A472">
+        <f t="shared" si="7"/>
+        <v>471</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1">
+      <c r="A473">
+        <f t="shared" si="7"/>
+        <v>472</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1">
+      <c r="A474">
+        <f t="shared" si="7"/>
+        <v>473</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1">
+      <c r="A475">
+        <f t="shared" si="7"/>
+        <v>474</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1">
+      <c r="A476">
+        <f t="shared" si="7"/>
+        <v>475</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1">
+      <c r="A477">
+        <f t="shared" si="7"/>
+        <v>476</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1">
+      <c r="A478">
+        <f t="shared" si="7"/>
+        <v>477</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1">
+      <c r="A479">
+        <f t="shared" si="7"/>
+        <v>478</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1">
+      <c r="A480">
+        <f t="shared" si="7"/>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1">
+      <c r="A481">
+        <f t="shared" si="7"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1">
+      <c r="A482">
+        <f t="shared" si="7"/>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1">
+      <c r="A483">
+        <f t="shared" si="7"/>
+        <v>482</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1">
+      <c r="A484">
+        <f t="shared" si="7"/>
+        <v>483</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1">
+      <c r="A485">
+        <f t="shared" si="7"/>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1">
+      <c r="A486">
+        <f t="shared" si="7"/>
+        <v>485</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1">
+      <c r="A487">
+        <f t="shared" si="7"/>
+        <v>486</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1">
+      <c r="A488">
+        <f t="shared" si="7"/>
+        <v>487</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1">
+      <c r="A489">
+        <f t="shared" si="7"/>
+        <v>488</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1">
+      <c r="A490">
+        <f t="shared" si="7"/>
+        <v>489</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1">
+      <c r="A491">
+        <f t="shared" si="7"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1">
+      <c r="A492">
+        <f t="shared" si="7"/>
+        <v>491</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1">
+      <c r="A493">
+        <f t="shared" si="7"/>
+        <v>492</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1">
+      <c r="A494">
+        <f t="shared" si="7"/>
+        <v>493</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1">
+      <c r="A495">
+        <f t="shared" si="7"/>
+        <v>494</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1">
+      <c r="A496">
+        <f t="shared" si="7"/>
+        <v>495</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1">
+      <c r="A497">
+        <f t="shared" si="7"/>
+        <v>496</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1">
+      <c r="A498">
+        <f t="shared" si="7"/>
+        <v>497</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1">
+      <c r="A499">
+        <f t="shared" si="7"/>
+        <v>498</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1">
+      <c r="A500">
+        <f t="shared" si="7"/>
+        <v>499</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1">
+      <c r="A501">
+        <f t="shared" si="7"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1">
+      <c r="A502">
+        <f t="shared" si="7"/>
+        <v>501</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1">
+      <c r="A503">
+        <f t="shared" si="7"/>
+        <v>502</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1">
+      <c r="A504">
+        <f t="shared" si="7"/>
+        <v>503</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1">
+      <c r="A505">
+        <f t="shared" si="7"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1">
+      <c r="A506">
+        <f t="shared" si="7"/>
+        <v>505</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1">
+      <c r="A507">
+        <f t="shared" si="7"/>
+        <v>506</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1">
+      <c r="A508">
+        <f t="shared" si="7"/>
+        <v>507</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1">
+      <c r="A509">
+        <f t="shared" si="7"/>
+        <v>508</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1">
+      <c r="A510">
+        <f t="shared" si="7"/>
+        <v>509</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1">
+      <c r="A511">
+        <f t="shared" si="7"/>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1">
+      <c r="A512">
+        <f t="shared" si="7"/>
+        <v>511</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1">
+      <c r="A513">
+        <f t="shared" si="7"/>
+        <v>512</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1">
+      <c r="A514">
+        <f t="shared" si="7"/>
+        <v>513</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1">
+      <c r="A515">
+        <f t="shared" si="7"/>
+        <v>514</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1">
+      <c r="A516">
+        <f t="shared" ref="A516:A579" si="8">A515+1</f>
+        <v>515</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1">
+      <c r="A517">
+        <f t="shared" si="8"/>
+        <v>516</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1">
+      <c r="A518">
+        <f t="shared" si="8"/>
+        <v>517</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1">
+      <c r="A519">
+        <f t="shared" si="8"/>
+        <v>518</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1">
+      <c r="A520">
+        <f t="shared" si="8"/>
+        <v>519</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1">
+      <c r="A521">
+        <f t="shared" si="8"/>
+        <v>520</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1">
+      <c r="A522">
+        <f t="shared" si="8"/>
+        <v>521</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1">
+      <c r="A523">
+        <f t="shared" si="8"/>
+        <v>522</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1">
+      <c r="A524">
+        <f t="shared" si="8"/>
+        <v>523</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1">
+      <c r="A525">
+        <f t="shared" si="8"/>
+        <v>524</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1">
+      <c r="A526">
+        <f t="shared" si="8"/>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1">
+      <c r="A527">
+        <f t="shared" si="8"/>
+        <v>526</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1">
+      <c r="A528">
+        <f t="shared" si="8"/>
+        <v>527</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1">
+      <c r="A529">
+        <f t="shared" si="8"/>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1">
+      <c r="A530">
+        <f t="shared" si="8"/>
+        <v>529</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1">
+      <c r="A531">
+        <f t="shared" si="8"/>
+        <v>530</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1">
+      <c r="A532">
+        <f t="shared" si="8"/>
+        <v>531</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1">
+      <c r="A533">
+        <f t="shared" si="8"/>
+        <v>532</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1">
+      <c r="A534">
+        <f t="shared" si="8"/>
+        <v>533</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1">
+      <c r="A535">
+        <f t="shared" si="8"/>
+        <v>534</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1">
+      <c r="A536">
+        <f t="shared" si="8"/>
+        <v>535</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1">
+      <c r="A537">
+        <f t="shared" si="8"/>
+        <v>536</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1">
+      <c r="A538">
+        <f t="shared" si="8"/>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="539" spans="1:1">
+      <c r="A539">
+        <f t="shared" si="8"/>
+        <v>538</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1">
+      <c r="A540">
+        <f t="shared" si="8"/>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1">
+      <c r="A541">
+        <f t="shared" si="8"/>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1">
+      <c r="A542">
+        <f t="shared" si="8"/>
+        <v>541</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1">
+      <c r="A543">
+        <f t="shared" si="8"/>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1">
+      <c r="A544">
+        <f t="shared" si="8"/>
+        <v>543</v>
+      </c>
+    </row>
+    <row r="545" spans="1:1">
+      <c r="A545">
+        <f t="shared" si="8"/>
+        <v>544</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1">
+      <c r="A546">
+        <f t="shared" si="8"/>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1">
+      <c r="A547">
+        <f t="shared" si="8"/>
+        <v>546</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1">
+      <c r="A548">
+        <f t="shared" si="8"/>
+        <v>547</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1">
+      <c r="A549">
+        <f t="shared" si="8"/>
+        <v>548</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1">
+      <c r="A550">
+        <f t="shared" si="8"/>
+        <v>549</v>
+      </c>
+    </row>
+    <row r="551" spans="1:1">
+      <c r="A551">
+        <f t="shared" si="8"/>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1">
+      <c r="A552">
+        <f t="shared" si="8"/>
+        <v>551</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1">
+      <c r="A553">
+        <f t="shared" si="8"/>
+        <v>552</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1">
+      <c r="A554">
+        <f t="shared" si="8"/>
+        <v>553</v>
+      </c>
+    </row>
+    <row r="555" spans="1:1">
+      <c r="A555">
+        <f t="shared" si="8"/>
+        <v>554</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1">
+      <c r="A556">
+        <f t="shared" si="8"/>
+        <v>555</v>
+      </c>
+    </row>
+    <row r="557" spans="1:1">
+      <c r="A557">
+        <f t="shared" si="8"/>
+        <v>556</v>
+      </c>
+    </row>
+    <row r="558" spans="1:1">
+      <c r="A558">
+        <f t="shared" si="8"/>
+        <v>557</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1">
+      <c r="A559">
+        <f t="shared" si="8"/>
+        <v>558</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1">
+      <c r="A560">
+        <f t="shared" si="8"/>
+        <v>559</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1">
+      <c r="A561">
+        <f t="shared" si="8"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1">
+      <c r="A562">
+        <f t="shared" si="8"/>
+        <v>561</v>
+      </c>
+    </row>
+    <row r="563" spans="1:1">
+      <c r="A563">
+        <f t="shared" si="8"/>
+        <v>562</v>
+      </c>
+    </row>
+    <row r="564" spans="1:1">
+      <c r="A564">
+        <f t="shared" si="8"/>
+        <v>563</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1">
+      <c r="A565">
+        <f t="shared" si="8"/>
+        <v>564</v>
+      </c>
+    </row>
+    <row r="566" spans="1:1">
+      <c r="A566">
+        <f t="shared" si="8"/>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1">
+      <c r="A567">
+        <f t="shared" si="8"/>
+        <v>566</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1">
+      <c r="A568">
+        <f t="shared" si="8"/>
+        <v>567</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1">
+      <c r="A569">
+        <f t="shared" si="8"/>
+        <v>568</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1">
+      <c r="A570">
+        <f t="shared" si="8"/>
+        <v>569</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1">
+      <c r="A571">
+        <f t="shared" si="8"/>
+        <v>570</v>
+      </c>
+    </row>
+    <row r="572" spans="1:1">
+      <c r="A572">
+        <f t="shared" si="8"/>
+        <v>571</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1">
+      <c r="A573">
+        <f t="shared" si="8"/>
+        <v>572</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1">
+      <c r="A574">
+        <f t="shared" si="8"/>
+        <v>573</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1">
+      <c r="A575">
+        <f t="shared" si="8"/>
+        <v>574</v>
+      </c>
+    </row>
+    <row r="576" spans="1:1">
+      <c r="A576">
+        <f t="shared" si="8"/>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1">
+      <c r="A577">
+        <f t="shared" si="8"/>
+        <v>576</v>
+      </c>
+    </row>
+    <row r="578" spans="1:1">
+      <c r="A578">
+        <f t="shared" si="8"/>
+        <v>577</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1">
+      <c r="A579">
+        <f t="shared" si="8"/>
+        <v>578</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DawesRollsViewer/Dawes Rolls One Document/Chickasaw/Chickasaw Newborn.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Chickasaw/Chickasaw Newborn.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="25">
   <si>
     <t>ID</t>
   </si>
@@ -77,6 +77,18 @@
   </si>
   <si>
     <t>Dawes Rolls Full Document - Chickasaw By Blood - Page 204</t>
+  </si>
+  <si>
+    <t>Image Name</t>
+  </si>
+  <si>
+    <t>Image Binary</t>
+  </si>
+  <si>
+    <t>Stricken From Roll</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -408,16 +420,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O579"/>
+  <dimension ref="A1:Q579"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
     <col min="12" max="12" width="20.140625" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
     <col min="14" max="14" width="51.140625" customWidth="1"/>
+    <col min="16" max="17" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -463,8 +476,14 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -481,7 +500,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -501,7 +520,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:17">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -521,7 +540,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -541,7 +560,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -561,7 +580,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:17">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -581,7 +600,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -601,7 +620,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -621,7 +640,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -641,7 +660,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -661,7 +680,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -681,7 +700,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:17">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -701,7 +720,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:17">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -721,7 +740,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:17">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -741,7 +760,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:17">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -11367,8 +11386,35 @@
         <f t="shared" si="28"/>
         <v>204</v>
       </c>
+      <c r="D547" t="s">
+        <v>23</v>
+      </c>
+      <c r="E547" t="s">
+        <v>24</v>
+      </c>
+      <c r="F547" t="s">
+        <v>24</v>
+      </c>
+      <c r="G547" t="s">
+        <v>24</v>
+      </c>
+      <c r="H547">
+        <v>-1</v>
+      </c>
+      <c r="I547" t="s">
+        <v>24</v>
+      </c>
+      <c r="J547" t="s">
+        <v>24</v>
+      </c>
+      <c r="K547" t="s">
+        <v>24</v>
+      </c>
       <c r="L547" t="s">
-        <v>15</v>
+        <v>24</v>
+      </c>
+      <c r="M547" t="s">
+        <v>24</v>
       </c>
       <c r="N547" t="str">
         <f t="shared" si="29"/>

--- a/DawesRollsViewer/Dawes Rolls One Document/Chickasaw/Chickasaw Newborn.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Chickasaw/Chickasaw Newborn.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -79,16 +79,19 @@
     <t>Dawes Rolls Full Document - Chickasaw By Blood - Page 204</t>
   </si>
   <si>
-    <t>Image Name</t>
-  </si>
-  <si>
-    <t>Image Binary</t>
-  </si>
-  <si>
     <t>Stricken From Roll</t>
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>ImageBinary</t>
+  </si>
+  <si>
+    <t>ImageName</t>
+  </si>
+  <si>
+    <t>TribeRelationship</t>
   </si>
 </sst>
 </file>
@@ -420,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q579"/>
+  <dimension ref="A1:R579"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
@@ -428,9 +431,10 @@
     <col min="13" max="13" width="10" customWidth="1"/>
     <col min="14" max="14" width="51.140625" customWidth="1"/>
     <col min="16" max="17" width="13.28515625" customWidth="1"/>
+    <col min="18" max="18" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,13 +481,16 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
+        <v>23</v>
+      </c>
+      <c r="R1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -500,7 +507,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -520,7 +527,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -540,7 +547,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -560,7 +567,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -580,7 +587,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -600,7 +607,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -620,7 +627,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -640,7 +647,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -660,7 +667,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -680,7 +687,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -700,7 +707,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -720,7 +727,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -740,7 +747,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -760,7 +767,7 @@
         <v>Dawes Rolls Full Document - Chickasaw By Blood - Page 201</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -11387,34 +11394,34 @@
         <v>204</v>
       </c>
       <c r="D547" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E547" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F547" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G547" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H547">
         <v>-1</v>
       </c>
       <c r="I547" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J547" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K547" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L547" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M547" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N547" t="str">
         <f t="shared" si="29"/>
